--- a/sources/ReadMe_NL.xlsx
+++ b/sources/ReadMe_NL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Temp\Python\weblate\digcomp3-l10n\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1358DB31-FE43-4A88-B6DE-5C4C802EC974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4120627-6201-4072-874E-FE9CD97B0CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-5400" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -206,12 +206,6 @@
     <t>Naam beheersingsniveau; Beschrijving beheersingsniveau (vier niveaus); Doel; Mapping acht niveaus; Mapping zes niveaus; Beschrijving beheersingsniveau (acht niveaus)</t>
   </si>
   <si>
-    <t>3 Competentiestellingen</t>
-  </si>
-  <si>
-    <t>Nummer competentiegebied; Naam competentiegebied; Omschrijving competentiegebied; Nummer competentie; Naam competentie; Omschrijving competentie; ID competentiestelling; Competentiestelling; Naam beheersingsniveau; AI-label</t>
-  </si>
-  <si>
     <t>4 Leerresultaten</t>
   </si>
   <si>
@@ -272,18 +266,9 @@
     <t>Nummer van elk van de 21 competenties van DigComp 3.0 in het formaat x.y, waarbij x het nummer van het competentiegebied aangeeft en y opeenvolgend loopt binnen de competentie. De drie competenties binnen competentiegebied 1 (informatie en data) zijn bijvoorbeeld genummerd 1.1, 1.2 en 1.3.</t>
   </si>
   <si>
-    <t>Competentiestelling</t>
-  </si>
-  <si>
     <t>Stellingen ingedeeld naar de 21 competenties en vier beheersingsniveaus van DigComp 3.0.</t>
   </si>
   <si>
-    <t>ID competentiestelling</t>
-  </si>
-  <si>
-    <t>Het ID van elke competentiestelling van DigComp 3.0, dat opeenvolgend loopt binnen elke competentie en het competentienummer bevat. Elk ID begint met 'CS'. Competentie 1.1 heeft bijvoorbeeld 15 competentiestellingen, CS1.1.01 tot CS1.1.15.</t>
-  </si>
-  <si>
     <t>Mapping acht niveaus</t>
   </si>
   <si>
@@ -368,13 +353,28 @@
     <t>De vertaling naar het Nederlands is uitgevoerd door het iXperium Centre of Expertise Teaching and Learning.</t>
   </si>
   <si>
-    <t>Vertaling: Gorissen, P. en van Zanten, M., DigComp 3.0 Nederlands, iXperium Centre of Expertise Leren met ict, Nijmegen, Nederland, 2026. https://ixperium.nl</t>
-  </si>
-  <si>
     <t>Creative Commons Attribution 4.0 International (CC BY 4.0) https://creativecommons.org/licenses/by/4.0/</t>
   </si>
   <si>
     <t>Licentie:</t>
+  </si>
+  <si>
+    <t>Vertaling: Gorissen, P. &amp; van Zanten, M., DigComp 3.0 Nederlands : Vertaling van het Digital Competence Framework for Citizens (DigComp). iXperium Centre of Expertise Leren met ict, Nijmegen, Nederland, 2026. https://ixperium.nl</t>
+  </si>
+  <si>
+    <t>3 Competentiebeschrijvingen</t>
+  </si>
+  <si>
+    <t>Het ID van elke competentieomschrijving van DigComp 3.0, dat opeenvolgend loopt binnen elke competentie en het competentienummer bevat. Elk ID begint met 'CS'. Competentie 1.1 heeft bijvoorbeeld 15 competentieomschrijvingen, CS1.1.01 tot CS1.1.15.</t>
+  </si>
+  <si>
+    <t>Competentiebeschrijving</t>
+  </si>
+  <si>
+    <t>ID competentiebeschrijving</t>
+  </si>
+  <si>
+    <t>Nummer competentiegebied; Naam competentiegebied; Omschrijving competentiegebied; Nummer competentie; Naam competentie; Omschrijving competentie; ID competentiebeschrijving; competentiebeschrijving; Naam beheersingsniveau; AI-label</t>
   </si>
 </sst>
 </file>
@@ -1078,7 +1078,7 @@
   <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.28515625" customWidth="1"/>
+    <col min="1" max="1" width="70.42578125" customWidth="1"/>
     <col min="2" max="2" width="220.7109375" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="8" max="8" width="5.5703125" customWidth="1"/>
@@ -1087,12 +1087,12 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1124,26 +1124,26 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>62</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1151,162 +1151,162 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -1314,7 +1314,7 @@
         <v>53</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1325,12 +1325,12 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1338,10 +1338,10 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -1349,24 +1349,24 @@
     </row>
     <row r="40" spans="1:2" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B40" s="22"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="22" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B43" s="22"/>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
